--- a/xlsx/tests/calc_tests/TEXTSPLIT.xlsx
+++ b/xlsx/tests/calc_tests/TEXTSPLIT.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhatcher/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C731B0B-8FDC-C34D-A616-152127868820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87922DDA-0094-044A-AE36-6583FFA0B21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1580" windowWidth="28040" windowHeight="17180" xr2:uid="{10A81E57-D5CC-1C4E-B7C4-B7168AC75F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Orange,Banana,Pear,Apple</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>1,2,3;2,3;4,5,6,7</t>
+  </si>
+  <si>
+    <t>Hola sin split</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B42C797-63E7-1644-ADF6-F1E042BDAFC8}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -685,7 +688,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <v>2</v>
       </c>
@@ -699,7 +702,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <v>4</v>
       </c>
@@ -713,7 +716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -731,7 +734,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
         <v>2</v>
       </c>
@@ -745,7 +748,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
         <v>4</v>
       </c>
@@ -757,6 +760,35 @@
       </c>
       <c r="E22" t="str">
         <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="e" cm="1">
+        <f t="array" ref="B26">_xlfn.TEXTSPLIT(A26,)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D26" t="e" cm="1">
+        <f t="array" ref="D26">_xlfn.TEXTSPLIT(A26,C26)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F26" t="e" cm="1">
+        <f t="array" ref="F26">_xlfn.TEXTSPLIT(A26,,C26)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H26" t="e" cm="1">
+        <f t="array" ref="H26">_xlfn.TEXTSPLIT(A26,"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J26" t="e" cm="1">
+        <f t="array" ref="J26">_xlfn.TEXTSPLIT(A26,,"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L26" t="e" cm="1">
+        <f t="array" ref="L26">_xlfn.TEXTSPLIT(A26,,)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
